--- a/dat/direttorio.xlsx
+++ b/dat/direttorio.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\CONGREGATION-APP\direttorio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\GITHUB REPO\fsmi\dat\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60FC045-119C-4065-83AF-76CCFAC74C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D5A08FD-27AF-436D-B309-FCE7D9148750}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4728" yWindow="1344" windowWidth="16620" windowHeight="11616" xr2:uid="{C4EA4354-D3C4-416A-B859-4048EF642DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{C4EA4354-D3C4-416A-B859-4048EF642DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="Direttorio" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Direttorio!$A$1:$G$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Direttorio!$A$1:$G$230</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="926" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="272">
   <si>
     <t>PART</t>
   </si>
@@ -63,12 +63,6 @@
     <t>text</t>
   </si>
   <si>
-    <t>Aggiornato dal XVIII Capitolo Generale - 2011</t>
-  </si>
-  <si>
-    <t>Italiano</t>
-  </si>
-  <si>
     <t>INTRODUZIONE</t>
   </si>
   <si>
@@ -96,60 +90,21 @@
     <t>CIC Codex Iuris Canonici</t>
   </si>
   <si>
-    <t>ed. edizione</t>
-  </si>
-  <si>
-    <t>MC Marialis Cultus, Esortazione apostolica di Paolo VI, per ravvivare il culto verso la Beata Vergine Maria, AAS 113, 1974</t>
-  </si>
-  <si>
     <t>O.A. Opere Ascetiche, del Venerabile Giuseppe Frassinetti, 2 voll., Roma 1978</t>
   </si>
   <si>
     <t>O.O. Opera Omnia, del Venerabile Giuseppe Frassinetti, 13 voll. ed. Vaticana, Roma 1908-1912</t>
   </si>
   <si>
-    <t>OT Optatam Totius, Decreto sulla formazione sacerdotale del Concilio Ecumenico Vaticano II</t>
-  </si>
-  <si>
-    <t>SCSacosantum Concilium, Costituzione sulla Sacra Liturgia del Concilio Ecumenico Vaticano II</t>
-  </si>
-  <si>
-    <t>ss. seguenti</t>
-  </si>
-  <si>
-    <t>TFRtrattamento di fine rapporto</t>
-  </si>
-  <si>
-    <t>vol.volume</t>
-  </si>
-  <si>
     <t>CAP 1. A MARIA IMMACOLATA MADRE DELLA CONGREGAZIONE</t>
   </si>
   <si>
     <t>canon</t>
   </si>
   <si>
-    <t>Maria, dopo Cristo, occupa nella Chiesa il posto più alto e il più vicino a noi; è il modello dell’atteggiamento spirituale con cui ogni Religioso ascolta, accoglie, proclama, venera la Parola di Dio e la dispensa ai fratelli come pane di Vita.</t>
-  </si>
-  <si>
-    <t>La pietà verso la Madre di Gesù è uno strumento efficace per giungere alla piena conoscenza del Figlio di Dio, fino a raggiungere la misura della piena statura di Cristo.</t>
-  </si>
-  <si>
-    <t>Il Figlio di Maria s’impegna a riprodurre i lineamenti spirituali di Gesù, che hanno animato il cuore della Vergine e si manifestano con attualità nelle virtù evangeliche: “La fede e l’accoglienza docile della Parola di Dio (cfr. Lc 1,26-38; 1,45; 11,27-28; Gv 2,5); l’obbedienza generosa (cfr. Lc 1,38); l’umiltà schietta (cfr. Lc 1,48); la carità sollecita (cfr. Lc 1,39-56); la sapienza riflessiva (cfr. Lc 1,29-34; 2,19.33.51) la pietà verso Dio, alacre nell’adempimento dei doveri religiosi (cfr. Lc 1,21.22-40.41) riconoscente dei doni ricevuti (cfr. Lc, 1,46-49), offerente nel tempio (cfr. Lc 1,22-24),orante nella comunità apostolica (cfr. At 1, 12-14); la fortezza nell’esilio (cfr. Mt 2, 13-23), nel dolore (cfr. Lc 2,34-35.49; Gv 19,25); la povertà dignitosa e fidente in Dio (cfr. Lc 1,48; 2,24); la vigile premura verso il Figlio, dall’umiliazione della culla fino all’ignominia della croce (cfr. Lc 2,1-7; Gv 19,35-27), la delicatezza previdente (cfr. Gv. 2,1-11); la purezza verginale (cfr. Mt 1,18-25; Lc 1,26-38)” (MC 57).</t>
-  </si>
-  <si>
-    <t>Il Figlio di Maria s’impegna coi mezzi più idonei a far crescere la conoscenza, l’amore e l’imitazione della Beata Vergine.</t>
-  </si>
-  <si>
     <t>Il Rosario deve essere la preghiera che favorisce lo spirito della comunità, che al termine della giornata si raduna per creare le condizioni della presenza del Signore. In questo modo la recita del Rosario assume un ritmo tranquillo e quasi un indugio pensoso che favorisce la meditazione dei misteri della vita del Signore, visti attraverso il cuore di Colei che al Signore fu più vicina.</t>
   </si>
   <si>
-    <t>Rimanga viva la pratica dell’Angelus quale invito ad una pausa di preghiera che segna il tempo della quotidiana attività.</t>
-  </si>
-  <si>
-    <t>La preghiera della sera in ogni casa della Congregazione si concluderà con il canto di un’antifona mariana.</t>
-  </si>
-  <si>
     <t>Al sabato e tutte le volte che è consentito dalle disposizioni liturgiche, si celebri la Messa della Madonna e se ne reciti l’Ufficio. La meditazione e la predicazione traducano la Parola di Dio in alimento di fede e di testimonianza.</t>
   </si>
   <si>
@@ -192,12 +147,6 @@
     <t>I Superiori, come padri, provvedano in tempo alle necessità dei confratelli, interrogandoli anche, di quando in quando, su quanto possa loro occorrere e procurando si ispirare a tutti confidenza; vigilino in pari tempo che non nascano abusi o arbitri personali.</t>
   </si>
   <si>
-    <t>La povertà religiosa non consente di tenere presso di sé, per proprio uso, somme personali di denaro, oggetti di lusso e tutto ciò che sa di vano e di superfluo. Abbia ciascuno nelle vesti e nelle suppellettili quanto è necessario per i suoi bisogni e per il suo decoro; si conformi in tutto alla vita comune e non cerchi mai riguardi e distinzioni.</t>
-  </si>
-  <si>
-    <t>Qualora necessitasse di vestiario, di libri, di cancelleria, di vitto speciale, di medicine o simili, si rivolga al Superiore o al confratello incaricato.</t>
-  </si>
-  <si>
     <t>I Sacerdoti, i Diaconi e i Fratelli coadiutori di voti perpetui avranno mese per mese una modesta somma per opere caritative e per piccole spese, determinata dal Capitolo generale. Detta somma non può essere accumulata. Per gli studenti religiosi e i novizi darà indicazioni il Superiore generale sentiti i Maestri.</t>
   </si>
   <si>
@@ -211,14 +160,6 @@
   </si>
   <si>
     <t>Di ogni atto avente effetto civile e legale il religioso invii copia all’Archivio generale per essere conservata nella posizione personale del confratello.</t>
-  </si>
-  <si>
-    <t>Le pensioni che provengono al Religioso per lavoro, per convenzione o altra ragione, pertinenti esclusivamente al periodo antecedente l’ingresso nella vita religiosa, fanno parte del suo patrimonio e vengono regolate a norma del can. 668 3 del CIC e dell’art. 95 delle Costituzioni.</t>
-  </si>
-  <si>
-    <t>Le pensioni che provengono al Religioso per lavoro svolto nel tempo trascorso nella vita religiosa, o per circostanze o condizioni pertinenti al medesimo tempo, e le pensioni dette in Italia “sociali” fanno parte dei beni comuni e saranno versate alla casa cui appartiene o alla casa generale, a giudizio del Superiore generale.
-E’ vivamente raccomandato che, ove si verifichino le necessarie condizioni, vengano compiute le prosecuzioni volontarie per far maturare i diritti alle pensioni. In questi casi se un Religioso ha iniziato forme assicurative prima di entrare nella vita religiosa, concorderà con il Superiore generale gli oneri della prosecuzione volontaria e il godimento della pensione; se, al contrario, la prosecuzione volontaria avviene per forme assicurative iniziate dopo l’ingresso nella vita religiosa, gli oneri assicurativi sono a carico della casa generale e alla stessa verranno versati i godimenti della pensione, salvo eccezioni a giudizio del Superiore generale in favore della casa cui appartiene il confratello.
-In casi dubbi o non previsti da quanto sopra esposto, saranno rimessi alla decisione del Superiore generale.</t>
   </si>
   <si>
     <t>Non è lecito a nessuno dei confratelli, anche se Superiori o Economi delle case, senza il previo consenso scritto del Superiore generale:</t>
@@ -242,12 +183,6 @@
     <t>La castità consacrata è segno e stimolo della carità e speciale sorgente di spiritualità e fecondità, allarga l’orizzonte dell’apostolato, approfondisce il senso della responsabilità, educa in lui, come espressione di una più alta e vasta paternità, una pienezza e delicatezza di sentimenti che grandemente lo arricchiscono.</t>
   </si>
   <si>
-    <t>Imitando l’esempio del Frassinetti, in tutte le relazioni, sia in casa che fuori, i Figli di S. Maria Immacolata mantengono sempre quel dignitoso riserbo che è proprio di chi attende alla perfezione religiosa e ha il dovere di testimoniare, soprattutto con l’esempio, l’eccellenza di questa virtù.</t>
-  </si>
-  <si>
-    <t>Ognuno cercherà di guardarsi anche da quanto potrebbe ingenerare agli occhi altrui qualche ombra al riguardo.</t>
-  </si>
-  <si>
     <t>I Religiosi si convincano che per superare situazioni psicologiche difficili e per non indulgere a facili compensazioni è necessaria la lealtà con se stessi e l’aiuto, anche non richiesto, di persone amiche e sperimentate.</t>
   </si>
   <si>
@@ -296,12 +231,6 @@
     <t>Per meglio comprendere e sentire il valore dell’obbedienza i Religiosi vivano un rapporto di fraterna unione e dialogo leale e rispettoso che assicuri e faciliti l’esercizio dell’autorità ed insieme la responsabilità dell’obbedienza.</t>
   </si>
   <si>
-    <t>Sappiano far tesoro delle occasioni che offrono la possibilità di praticare in concreto la virtù dell’obbedienza, superando le umane riluttanze con spirito di sacrificio.</t>
-  </si>
-  <si>
-    <t>Quando si riceve l’ordine di mutare casa o ufficio, si attui l’obbedienza con generosità, anche se non appaiono evidenti i motivi dell’ordine ricevuto.</t>
-  </si>
-  <si>
     <t>Quando si vedesse un confratello in difficoltà nella pratica dell’obbedienza lo si aiuti fraternamente ad attuarla con il consiglio e la preghiera.</t>
   </si>
   <si>
@@ -347,12 +276,6 @@
     <t>(cfr. Costituzioni art. 131ss)</t>
   </si>
   <si>
-    <t>I confratelli pratichino specialmente la carità fraterna, siano l’un l’altro di reciproca emulazione nella pratica delle virtù religiose ed accolgano con umiltà e gratitudine la correzione fraterna, fatta loro secondo lo spirito del Vangelo.</t>
-  </si>
-  <si>
-    <t>Si mostrino sempre, con tutti, sereni, comprensivi e fraternamente aperti.</t>
-  </si>
-  <si>
     <t>Chi sentirà d’aver offeso un confratello o crederà d’aver ricevuto offesa, curi con premura e con la maggior larghezza di cuore che la mutua carità non abbia a risentirne.</t>
   </si>
   <si>
@@ -395,31 +318,13 @@
     <t>(cfr. Costituzioni art. 145ss)</t>
   </si>
   <si>
-    <t>Si raccomanda che nella parte della casa riservata ai religiosi, eccetto che per lavori e pulizie, non siano ammesse persone estranee alla comunità.</t>
-  </si>
-  <si>
-    <t>Per le ripetizioni a persone singole siano destinati, dal Superiore o da chi di dovere , locali soggetti a controllo.</t>
-  </si>
-  <si>
     <t>Anche nelle uscite, nelle visite, nei viaggi, nell’uso degli automezzi i confratelli ricordino sempre che sono Religiosi, impegnati cioè a dar testimonianza del consigli evangelici per amore di Gesù Cristo.</t>
   </si>
   <si>
-    <t>E’ opportuno che tutti i Religiosi trascorrano nell’anno un periodo di vacanze per complessivi 20 giorni, in famiglia o in case della Congregazione, oppure in altro luogo di soggiorno concordato con il Superiore locale e la comunità. I confratelli Sacerdoti e i Fratelli professi che risiedono fuori dal proprio continente trascorreranno ogni due anni un periodo di 30 giorni nella propria nazione, Per le vacanze sarà elargita ai confratelli una congrua somma del cui impiego renderanno poi conto al Superiore. La somma per le vacanze, eccettuata quella del viaggio, sia uguale per tutti i confratelli e sia stabilita dal Consiglio Superiore.</t>
-  </si>
-  <si>
-    <t>Le vacanze degli studenti professi, sia in patria che nelle nostre comunità, essendo un periodo positivo nell’iter formativo del giovane religioso, saranno regolamentate dal Consiglio Superiore in accordo con il Formatore.</t>
-  </si>
-  <si>
     <t>Siano particolarmente prudenti nel fare visite o nell’accogliere inviti da famiglie di alunni o dipendenti, sapendo come e quanto esse possano dare adito a interpretazioni non benevole o condizionare l’azione propria e degli altri.</t>
   </si>
   <si>
     <t>I confratelli, anche quelli impegnati nel ministero, procurino di essere presenti per i principali atti di comunità.</t>
-  </si>
-  <si>
-    <t>Non si viaggi se non per giusti motivi, evitando spese non richieste dalla necessità e non consone alla povertà.</t>
-  </si>
-  <si>
-    <t>Se i confratelli si fermeranno in luoghi ove esiste una nostra casa, preferibilmente alloggeranno in essa.</t>
   </si>
   <si>
     <t>Se alcuno dovrà mettersi in viaggio o dimorare qualche tempo fuori delle case della Congregazione riceverà, oltre l’importo delle spese previste, una conveniente somma di riserva per le possibili occorrenze impreviste. Al ritorno, o all’arrivo se si tratta di trasferimento, il confratello renda conto delle spese al Superiore.</t>
@@ -487,83 +392,16 @@
     <t>(cfr. Costituzioni art. 171ss)</t>
   </si>
   <si>
-    <t>L’Istituto di educazione e istruzione è affidato all’intera comunità religiosa educante.</t>
-  </si>
-  <si>
-    <t>Essa è costituita in forma primaria dai Religiosi che operano nell’istituto, affiancati in un rapporto di collaborazione e integrazione dai laici che, a vario titolo, sono coinvolti nell’opera educativa e formativa dell’istituto stesso.</t>
-  </si>
-  <si>
-    <t>Negli istituti di istruzione vi sia possibilmente un preside per le scuole di 1° grado, un preside per le scuole di 2° grado e un responsabile per le scuole elementari.</t>
-  </si>
-  <si>
-    <t>Essi sono nominati dal Superiore generale e suo Consiglio, sentito il parere del Superiore locale.</t>
-  </si>
-  <si>
     <t>Ogni istituto d’istruzione sia corredato di adeguate strutture e attrezzature didattiche.</t>
   </si>
   <si>
     <t>Quando si venisse proposti alla direzione di seminari o di altri istituti di formazione ecclesiale non appartenenti alla Congregazione, nel loro governo si seguiranno le norme degli articoli precedenti, salvo la diretta dipendenza dai Vescovi a norma delle disposizioni ecclesiastiche vigenti.</t>
   </si>
   <si>
-    <t>Siano costituite in tutte le case o istituti d’educazione e di istruzione le associazioni degli ex-allievi per continuare l’opera di formazione in vista dell’azione educativa da estendere nelle loro famiglie.</t>
-  </si>
-  <si>
-    <t>La comunità demandi al Religioso ritenuto più idoneo l’assistenza dell’associazione.
-A) Il Superiore
-90. Il Superiore è il coordinatore dell’andamento spirituale, scolastico, disciplinare ed economico dell’istituto. I confratelli chiamati a collaborare con lui sono responsabili ciascuno del proprio ufficio: “Tale autonomia però non è assoluta: implica sempre obbedienza responsabile e ordinata e comporta il collegamento con l’autorità del Superiore e la dipendenza da essa” (cfr. art. 194 delle Costituzioni).
-91. Nella direzione e governo dell’istituto, il Superiore dovrà procedere d’intesa con i suoi collaboratori nella programmazione delle attività fondamentali e del lavoro dei confratelli.
-92. E’ compito specifico del Superiore dare precisi indirizzi perché l’istituto consegua il fine a cui è destinato e accertarsi che l’insegnamento impartito nella scuola sia in linea con il nostro carisma ed in armonia con le più sane tradizioni della scuola cattolica secondo le indicazioni del magistero della Chiesa e delle Conferenze Episcopali.
-93. Ricordando lo scopo vocazionale della nostra Congregazione, il Superiore procuri di favorire le vocazioni sacerdotali e religiose, appoggiando le iniziative dei vocazionisti e del padre spirituale.
-94. Si regolerà in tutto secondo le mansioni e le responsabilità attribuitegli dalle Costituzioni e dal presente Direttorio.
-95. Il Superiore assumerà anche la funzione di gestore “durante munere” dell’istituto scolastico annesso alla casa religiosa.
-96. Il Superiore si adoperi perché tra i presidi regni la più cordiale collaborazione per l’unità educativa dell’istituto e per il coordinamento delle varie attività dell’anno scolastico.
-97. Gli alunni del convitto dipendono dal Superiore, al quale spettano anche l’accettazione e il licenziamento di essi come pure il trattare con i loro parenti e tutori.
-Le rette e i criteri per le eventuali riduzioni ad alunni meritevoli ma bisognosi saranno stabilite d’intesa con la comunità.
-98. Il Superiore con la generosa e fattiva collaborazione di tutta la comunità darà grande importanza alla vita spirituale favorendo la partecipazione degli alunni alla celebrazione dell’Eucarestia, la frequenza ai Sacramenti, ai momenti di preghiera e di adorazione e la devozione filiale a Maria Immacolata.
-99. Per la parte disciplinare eserciterà una generale vigilanza senza intervenire direttamente nelle cose secondarie e minute affidate ai suoi collaboratori.
-Avrà fiducia in loro e concederà la libertà d’azione nell’ambito del loro ufficio, curando che lo adempiano con esattezza.
-100. In ogni circostanza si comporti in maniera da ispirare confidenza e fiducia. Si adoperi nell’eliminare, anzi prevenire, ogni causa di giustificato malcontento fra gli alunni.
-101. Qualora situazioni particolari richiedessero di affiancare al Superiore un altro confratello che assuma responsabilità specifiche nella coordinazione dell’attività dell’istituto, il Superiore generale, consultato il Superiore della casa, provvederà a nominare un confratello a tale scopo.
-B) I Presidi
-102. I Presidi adempiano il loro ufficio in conformità alle leggi vigenti e alle direttive delle superiori autorità religiose.
-Curino, secondo il progetto educativo della Congregazione, la formazione degli alunni e la sensibilità degli insegnanti esterni per l’apostolato cristiano della scuola.
-Il vice-preside sia di preferenza un insegnante religioso della comunità, con firma depositata al provveditorato.
-103. L’insegnamento della religione, anima e direttiva costante del nostro sistema educativo, sarà inserto nell’orario scolastico e attuato in due ore settimanali, specie nelle classi superiori.
-Ad esso saranno assegnati insegnanti ben preparati anche didatticamente ed efficacemente sostenuti dalla presidenza. Quanto è stato detto per i presidi vale anche per i responsabili delle scuole elementari.
-104. Sia i presidi i responsabili della scuola elementare riferiscano al Superiore sull’attività didattica degli insegnanti e sull’andamento didattico e disciplinare della scuola.
-105. Spetta al preside l’accettazione e il licenziamento degli insegnanti e degli alunni, sentito prima il parere e le proposte del Superiore e dell’Economo.
-C) Inseganti laici
-106. Gli insegnanti laici, preziosi collaboratori nelle nostre scuole, siano scelti tra persone non solo qualificate professionalmente, ma anche di elevati sentimenti morali e religiosi e di condotta seria e dignitosa.
-107. Con opportune istruzioni si curi:
-•. che siano animati da spirito di apostolato, base indispensabile di ogni efficace azione educativa ed istruttiva;
-•. che sentano l’altezza del loro compito e lo compiano con dignità e competenza, nella convinzione che è soprattutto con l’esempio che si formano i giovani.
-108. All’atto della loro assunzione sia stipulato un regolare contratto di lavoro, secondo il modulo della categoria e si osservino tutte le prescrizioni di leggere per quanto concerne le assicurazioni sociali e il trattamento economico.
-109. Si accantoni per ciascuno ogni anno almeno una mensualità del loro stipendio, al fine di costituire un adeguato fondo di liquidazione. Se qualcuno dovesse essere licenziato, gli si dia il necessario preavviso, secondo contratto, gli si liquidino con giustizia tutte le sue spettanze e si procuri di rimanere con lui in buone relazioni di amicizia.
-D) Il Padre Spirituale
-110. Il Padre spirituale nei nostri istituti è il consigliere e la guida spirituale degli alunni e il collaboratore ordinario del Superiore per l’organizzazione delle attività religiose dei giovani.
-111. Il Padre spirituale terrà in massima considerazione e stima il suo ufficio e vi si dedicherà invocando l’aiuto del Signore e applicandovisi con diligenza e sacrificio. Procurerà de perfezionare continuamente quelle doti soprannaturali e naturali che gli permettano un più facile avvicinamento ai giovani, quali la sensibilità psicologica, l’apertura umana del cuore, l’equilibrio interiore, la sua vita spirituale stessa.
-112. Triplice è il suo compito:
-a. la formazione comune che riguarda tutti gli alunni e si attua nelle pratiche comuni di pietà: vita sacramentale, santa Messa, meditazione, esercizi spirituali, ecc.;
-b. la formazione personale che riguarda il singolo alunno e che si attua con il colloquio, la confessione, la direzione spirituale propriamente detta;
-c. la formazione specializzata che raggiunge quei gruppi di alunni che desiderano impegnarsi più attivamente nella vita di apostolato e di perfezione.
-113. Cercherà, con i mezzi più idonei e più comprovati dalla scienza pastorale e dall’esperienza, di ottenere una convinta formazione cristiana dei giovani, cosicché sia assicurato un prosieguo di vita integralmente conforme ai principi del Vangelo.
-114. Con tatto e prudenza procuri che i ragazzi partecipino volenterosamente e consapevolmente anche alle necessarie pratiche comuni da compiersi in corrispondenza alle esigenze dell’età evolutiva dei giovani stessi.
-115. Egli dovrà favorire le devozioni specifiche e tradizionali dei Figli di S. Maria Immacolata, quali la devozione al S. Cuore, all’Immacolata, a S. Giuseppe e S. Pio X.
-116. Previa intesa con il Superiore, curerà l’organizzazione di incontri e si varrà di altri mezzi idonei a tenere la vita spirituale dei ragazzi nel periodo delle vacanze.
-Avrà premure particolari per gli alunni infermi.
-117. Vi sia piena collaborazione tra il Superiore e gli altri confratelli preposti alle varie attività della casa e il padre spirituale, cosicché non si frappongano reciproci impedimento, ma si consegua più facilmente il comune intento dell’integrale formazione del giovane.</t>
-  </si>
-  <si>
     <t>CAP 12. LE PARROCCHIE</t>
   </si>
   <si>
     <t>(cfr. Costituzioni art. 179ss)</t>
-  </si>
-  <si>
-    <t>Le nostre parrocchie sono determinate comunità di fedeli in cui si rende visibile in un certo modo la Chiesa universale e la cui cura pastorale è affidata dal Vescovo diocesano alla Congregazione dei Figli di Santa Maria Immacolata.</t>
-  </si>
-  <si>
-    <t>I Superiori delegheranno ad essa dei Religiosi che con la loro preghiera, vita comunitaria e osservanza dei voti religiosi attueranno la prima ed essenziale forma di evangelizzazione.</t>
   </si>
   <si>
     <t>Lo stile della vita religiosa nella parrocchia sia caratterizzato da una spiritualità che educhi a concepire la loro vita consacrata come vocazione, nel senso di una continua risposta ad una continua chiamata. Pertanto i Religiosi sono continuamente chiamati a rileggere e riscrivere la vita consacrata nella chiesa locale come</t>
@@ -574,38 +412,10 @@
 •. presenza di una nuova evangelizzazione.</t>
   </si>
   <si>
-    <t>Si tenga presente che nella parrocchia affidata, per mezzo della Congregazione, ad una comunità religiosa, tutti i confratelli sono corresponsabili della cura pastorale. Giuridicamente però un Religioso sarà designato come parroco e gli altri come vicari parrocchiali. Ai Religiosi addetti alla cura pastorale si garantisca una certa stabilità, ma si riconosce anche molto opportuno l’avvicendamento, tenendo presente il bene della Congregazione, le esigenze della parrocchia, l’orientamento degli episcopati nazionali.</t>
-  </si>
-  <si>
-    <t>Tuttavia è bene stare sempre alla retta intenzione e al discernimento del Superiore generale.</t>
-  </si>
-  <si>
     <t>I Confratelli addetti alle parrocchie curino i segni liturgici, vera catechesi ai fedeli, si tengano aggiornati con studi personali e con la partecipazione a convegni di pastorale. Trattino sia comunitariamente sia in unione con il consiglio pastorale i problemi della parrocchia tracciando le linee principali de organizzazione dell’apostolato. Si tenga presente che la vita comune da Religiosi è motore e modello di ogni attività apostolica nella vita parrocchiale ed è la testimonianza più efficace, soprattutto nei momenti di preghiera.</t>
   </si>
   <si>
-    <t>Nelle relazioni con le autorità ecclesiastiche, religiose e civili il parroco e i suoi collaboratori si mostrino rispettosi.</t>
-  </si>
-  <si>
-    <t>Nei rapporti con la popolazione si mantengano il più possibile al di sopra dei partiti e delle competizioni politiche. Tengano conto che la scelta preferenziale della Chiesa è verso i poveri.</t>
-  </si>
-  <si>
-    <t>Sia impegno caratteristico delle parrocchie dei Figli di S. Maria Immacolata curare una pastorale vocazionale non solo di annuncio deciso dei valori cristiani fondamentali, ma anche di accompagnamento attraverso la direzione spirituale.</t>
-  </si>
-  <si>
-    <t>Si studino anche iniziative per valorizzare tutto ciò che può favorire una crescita di coscienza vocazionale nei fedeli.
-Si raccomanda l’ascolto dei suggerimenti proposti dai nostri responsabili vocazionali.</t>
-  </si>
-  <si>
-    <t>Seguendo le indicazioni del Papa e dei Vescovi, si abbia un atteggiamento di apertura e di accettazione nei confronti dei movimenti ecclesiali tendenti a vitalizzare il laicato cattolico, vedendo in essi degli strumenti pastorali suscitati dallo Spirito Santo e adeguati al nostro tempo. Tuttavia i Religiosi si ricordino di essere i pastori di tutto il gregge di Dio a loro affidato, non assolutizzando le varie esperienze. Si fa presente la necessità della cura sistematica ed attenta dei gruppi giovanili della parrocchia affinché ogni seme di vocazione venga riconosciuto e curato.</t>
-  </si>
-  <si>
     <t>Quali educatori i Figli di S. Maria Immacolata impostino nelle parrocchie opere valide per la gioventù. Le attività culturali, ricreati, sportive siano ben dirette, seguite e finalizzate a orientare i giovani verso la comunità ecclesiale per aiutarli a vivere in modo sincero e convinto il Vangelo.</t>
-  </si>
-  <si>
-    <t>Ogni comunità deve darsi una pastorale concordata e studiata all’interno della comunità stessa nella quale si evidenzieranno con forza, anche attraverso le visite del Superiore generale, gli elementi fondamentali del carisma della Congregazione.</t>
-  </si>
-  <si>
-    <t>Non si potrà mai disattendere che, in ultima istanza, chi renderà visibile e tangibile il carisma della Congregazione sarà sempre il Figlio di Maria come testimone con le parole e con il suo stile di vita.</t>
   </si>
   <si>
     <t>Viene auspicato l’ascolto di quanto i Vescovi italiani da tempo vanno suggerendo, per determinate zone omogenee, di concordare delle linee pastorali comuni e questo come aiuto vicendevole e possibilità di scambio.</t>
@@ -626,13 +436,6 @@
     <t>E’ bene che intorno alla Congregazione ci sia un clima di simpatia, di amicizia e di amore. Ogni comunità deve trovare modi ed espressioni, le più favorevoli, perché questo si realizzi.</t>
   </si>
   <si>
-    <t>I rapporti tra comunità religiosa ed ente parrocchia saranno regolati dalla relativa convenzione tra Vescovo e Congregazione. Casi particolari saranno risolti dal Superiore generale e suo Consiglio, sentito il parere della comunità religiosa. Nelle spese straordinarie il parroco, oltre alle autorizzazioni scritte da parte del Vescovo, consulti il Superiore locale e, se fossero di notevole impegno, anche il Consiglio generale.</t>
-  </si>
-  <si>
-    <t>Non è lecito ai parroci contrarre impegni, servitù, contratti di qualsiasi genere su immobili della parrocchia, senza l’autorizzazione scritta dell’Ordinario diocesano, segnalando preventivamente la situazione al Superiore generale.
-Detto obbligo ricorre anche nelle variazioni di confine o di finalità dell’opera.</t>
-  </si>
-  <si>
     <t>L’ente parrocchia sia amministrato dal Consiglio parrocchiale per gli affari economici secondo le norme dei Vescovi. Del suddetto Consiglio fanno parte i Religiosi giuridicamente addetti alla parrocchia. L’amministrazione sia tenuta distinta da quella della casa religiosa.</t>
   </si>
   <si>
@@ -642,12 +445,6 @@
     <t>Alla fine di ogni anno solare si presenti al Consiglio generale la relazione amministrativa firmata dal Consiglio per gli affari economici della parrocchia.</t>
   </si>
   <si>
-    <t>I registri canonici saranno aggiornati e curati secondo le norme dell’Ordinario diocesano. Si tenga aggiornata la cronaca degli avvenimenti principali della parrocchia. Per questi si usino gli accorgimenti tecnici che si riterranno più idonei.</t>
-  </si>
-  <si>
-    <t>E’ auspicabile per la corrispondenza di ufficio parrocchiale l’uso del registro protocollo.</t>
-  </si>
-  <si>
     <t>Le nostre parrocchie all’estero seguiranno le indicazioni del proprio Statuto o le norme emanate dal Consiglio superiore.</t>
   </si>
   <si>
@@ -691,12 +488,6 @@
   </si>
   <si>
     <t>(cfr. Costituzioni art. 297ss)</t>
-  </si>
-  <si>
-    <t>Le case particolari attenderanno alle opere cui sonno state destinate. Non si potranno iniziare altre opere, nell’interno o fuori di dette case, sopprimere quelle esistenti o comunque modificarne lo scopo senza il consenso del Consiglio superiore.</t>
-  </si>
-  <si>
-    <t>Lo stesso deve essere ragguagliato tempestivamente qualora si verifichino eventi che possano comprometterne l’efficienza, l’economia e le finalità.</t>
   </si>
   <si>
     <t>Il Religioso al quale viene affidato l’incarico di Superiore di una comunità ponga a fondamento della sua attività i seguenti principi:</t>
@@ -722,12 +513,6 @@
     <t>Personalmente o per mezzo di un confratello scriverà la cronaca, annotando i fatti più importanti della giornata con sobrietà, ma tralasciando quelli che avessero carattere intimo o non fosse conveniente rendere pubblici tra i confratelli.</t>
   </si>
   <si>
-    <t>Con particolare cura preparerà la relazione annuale da inviare al Consiglio superiore, secondo le indicazioni fissate dal Capitolo o dal Consiglio stesso.</t>
-  </si>
-  <si>
-    <t>La suddetta relazione si invii unitamente al bilancio consuntivo e preventivo della casa.</t>
-  </si>
-  <si>
     <t>I confratelli professi di voti perpetui non hanno autorità per intervenire direttamente a dare ordini o disposizioni, ma dovranno coadiuvare il Superiore locale con il loro consiglio nel governo della comunità.</t>
   </si>
   <si>
@@ -737,12 +522,6 @@
     <t>Il Superiore, pur giovandosi del consiglio dei confratelli professi di voti perpetui nei casi indicati dalle Costituzioni e da questo Direttorio, dia grande importanza a tutta la comunità, trattando in comune i problemi della casa e favorendo lo spirito di responsabilità di ogni confratello.</t>
   </si>
   <si>
-    <t>Il Superiore, responsabile della comunità, vigilerà affinché i laici in qualche modo operanti alle dipendenze nelle nostre opere, siano di retti principi religiosi, di onesta condotta morale e, se conviventi nelle nostre case, disponibili all’osservare gli ordinamenti della casa stessa.</t>
-  </si>
-  <si>
-    <t>Ciò sia ben chiaro nel contratto di assunzione e sia convenuto come ragione valida di licenziamento in caso di inosservanza.</t>
-  </si>
-  <si>
     <t>CAP 15. IL MAESTRO DEI NOVIZI</t>
   </si>
   <si>
@@ -776,18 +555,6 @@
     <t>Ogni Ente giuridici è rappresentato da un soggetto debitamente qualificato, denominato Legale Rappresentante.</t>
   </si>
   <si>
-    <t>Spetta al Superiore generale e suo Consiglio, sentito prima il candidato, compiere la nomina del Legale Rappresentante.</t>
-  </si>
-  <si>
-    <t>Potrà essere nominato un Legale Rappresentante per ogni Ente giuridico, oppure più Enti giuridici potranno essere rappresentanti da un solo incaricato.</t>
-  </si>
-  <si>
-    <t>Il Legale Rappresentante rappresenta l’Ente religioso agli effetti giuridici e agisce in suo nome, tenendo presente che per il compimento di atti di straordinaria amministrazione (acquisti, vendite, locazioni, ipoteche, mutui...) o di particolare interesse, è necessaria l’autorizzazione del Superiore competente, secondo le Costituzioni e il Direttorio, nonché della Santa Sede, laddove è prescritta.</t>
-  </si>
-  <si>
-    <t>Si ponga particolare attenzione al rilievo giuridico del Legale Rappresentante per tutti gli atti di sua competenza e sia debitamente consultato.</t>
-  </si>
-  <si>
     <t>CAP 17. AMMINISTRAZIONE DEI BENI</t>
   </si>
   <si>
@@ -801,13 +568,6 @@
   </si>
   <si>
     <t>Il metodo di contabilità per ogni amministrazione sarà a norma di legge e secondo le direttive del Consiglio generale.</t>
-  </si>
-  <si>
-    <t>Fermi restando gli obblighi e le scadenze fissate da leggi civili ed ecclesiastiche per l’attività ad esse soggette, l’esercizio finanziario per le opere della Congregazione seguirà l’anno solare.</t>
-  </si>
-  <si>
-    <t>Per casi particolari, come gli istituti di istruzione, il Superiore generale e suo Consiglio potranno decidere diversamente.
-Il rendiconto annuale dell’esercizio finanziario e suo riscontro cassa documentato sarà inviato al Consiglio superiore entro tre mesi dalla scadenza secondo le forme indicate dalla Congregazione.</t>
   </si>
   <si>
     <t>I libretti di deposito, i conti correnti, i titoli di credito, eventuali depositi a custodia presso gli istituti bancari siano intestati agli Enti della Congregazione (legalmente riconosciuti) e le firme depositate non siano inferiori a due.</t>
@@ -818,12 +578,6 @@
   </si>
   <si>
     <t>Le case nelle quali si svolgono attività soggette alle leggi fiscali devono costituirsi un patrimonio di protezione per sostenere gli oneri e le spese richieste per un sano adempimento del lavoro esplicato, in modo particolare l’accantonamento per il “trattamento di fine apporto” (TFR).</t>
-  </si>
-  <si>
-    <t>Il contributo alla Cassa generale delle singole opere sarà annualmente stabilito dal Superiore generale e suo Consiglio, casa per casa, tenendo conto degli utili (e delle perdite) dell’anno precedente e del suo stato patrimoniale.</t>
-  </si>
-  <si>
-    <t>Le comunità siano sensibili alle esigenze della Congregazione, rispondendo con vero spirito religioso a quanto viene loro richiesto.</t>
   </si>
   <si>
     <t>Le case di formazione che dipendono dalla cassa generale avranno trimestralmente l’anticipo secondo i costi preventivati. Al termine dell’esercizio sarà cura della cassa generale pareggiare il rendiconto nell’ambito del piano preventivato.</t>
@@ -861,12 +615,6 @@
 c. l’Economo ne curerà l’esecuzione; eventuali modifiche o aggiunte di rilievo dovranno essere preventivamente approvate con la procedura precedente.</t>
   </si>
   <si>
-    <t>In ogni rapporto con i fornitori, ente, familiari degli alunni e con il personale di servizio l’Economo sappia manifestare sempre le più belle qualità umane e religiose, specie la gentilezza e la comprensione.</t>
-  </si>
-  <si>
-    <t>Ciò non gli impedirà di salvaguardare i diritti della casa religiosa, anzi gli renderà più facile il suo compito, dandogli l’occasione di offrire buona testimonianza religiosa. Sappia specialmente dare egli stesso grande importanza alle virtù della giustizia e della carità.</t>
-  </si>
-  <si>
     <t>CAP 19. CURA DEI LUOGHI SACRI</t>
   </si>
   <si>
@@ -894,12 +642,6 @@
     <t>Le norme del presente Direttorio, essendo state approvate dal Capitolo generale, non potranno essere modificate che da un altro Capitolo.</t>
   </si>
   <si>
-    <t>Al Superiore generale è lasciata facoltà di dispensare temporaneamente e per giusti e proporzionati motivi, tutta la Congregazione da qualcuna di esse.</t>
-  </si>
-  <si>
-    <t>La stessa facoltà e dentro gli stessi limiti è concessa al Superiore locale per la sua comunità.</t>
-  </si>
-  <si>
     <t>Sebbene le norme del Direttorio, salvo la materia dei voti e lo scandalo, non obblighino sotto pena di peccato, pure se ne raccomanda vivamente la precisa osservanza come mezzo di armoniosa vita comunitaria e valido strumento per raggiungere la perfezione religiosa.</t>
   </si>
   <si>
@@ -910,6 +652,272 @@
   </si>
   <si>
     <t>DIRETTORIO</t>
+  </si>
+  <si>
+    <t>ed.  edizione</t>
+  </si>
+  <si>
+    <t>MC  Marialis Cultus, Esortazione apostolica di Paolo VI, per ravvivare il culto verso la Beata Vergine Maria, AAS 113, 1974</t>
+  </si>
+  <si>
+    <t>OT    Optatam Totius, Decreto sulla formazione sacerdotale del Concilio Ecumenico Vaticano II</t>
+  </si>
+  <si>
+    <t>SC     Sacosantum Concilium, Costituzione sulla Sacra Liturgia del Concilio Ecumenico Vaticano II</t>
+  </si>
+  <si>
+    <t>ss.     seguenti</t>
+  </si>
+  <si>
+    <t>TFR   trattamento di fine rapporto</t>
+  </si>
+  <si>
+    <t>vol.   volume</t>
+  </si>
+  <si>
+    <t>Maria, dopo Cristo, occupa nella Chiesa il posto più alto e il più vicino a noi; è il modello dell’atteggiamento spirituale con cui ogni Religioso ascolta, accoglie, proclama, venera la Parola di Dio e la dispensa ai fratelli come pane di Vita.
+La pietà verso la Madre di Gesù è uno strumento efficace per giungere alla piena conoscenza del Figlio di Dio, fino a raggiungere la misura della piena statura di Cristo.</t>
+  </si>
+  <si>
+    <t>Il Figlio di Maria s’impegna a riprodurre i lineamenti spirituali di Gesù, che hanno animato il cuore della Vergine e si manifestano con attualità nelle virtù evangeliche: “La fede e l’accoglienza docile della Parola di Dio (cfr. Lc 1,26-38; 1,45; 11,27-28; Gv 2,5); l’obbedienza generosa (cfr. Lc 1,38); l’umiltà schietta (cfr. Lc 1,48); la carità sollecita (cfr. Lc 1,39-56); la sapienza riflessiva (cfr. Lc 1,29-34; 2,19.33.51) la pietà verso Dio, alacre nell’adempimento dei doveri religiosi (cfr. Lc 1,21.22-40.41) riconoscente dei doni ricevuti (cfr. Lc, 1,46-49), offerente nel tempio (cfr. Lc 1,22-24),orante nella comunità apostolica (cfr. At 1, 12-14); la fortezza nell’esilio (cfr. Mt 2, 13-23), nel dolore (cfr. Lc 2,34-35.49; Gv 19,25); la povertà dignitosa e fidente in Dio (cfr. Lc 1,48; 2,24); la vigile premura verso il Figlio, dall’umiliazione della culla fino all’ignominia della croce (cfr. Lc 2,1-7; Gv 19,35-27), la delicatezza previdente (cfr. Gv. 2,1-11); la purezza verginale (cfr. Mt 1,18-25; Lc 1,26-38)” (MC 57).
+Il Figlio di Maria s’impegna coi mezzi più idonei a far crescere la conoscenza, l’amore e l’imitazione della Beata Vergine.</t>
+  </si>
+  <si>
+    <t>Rimanga viva la pratica dell’Angelus quale invito ad una pausa di preghiera che segna il tempo della quotidiana attività.
+La preghiera della sera in ogni casa della Congregazione si concluderà con il canto di un’antifona mariana.</t>
+  </si>
+  <si>
+    <t>La povertà religiosa non consente di tenere presso di sé, per proprio uso, somme personali di denaro, oggetti di lusso e tutto ciò che sa di vano e di superfluo. Abbia ciascuno nelle vesti e nelle suppellettili quanto è necessario per i suoi bisogni e per il suo decoro; si conformi in tutto alla vita comune e non cerchi mai riguardi e distinzioni.
+Qualora necessitasse di vestiario, di libri, di cancelleria, di vitto speciale, di medicine o simili, si rivolga al Superiore o al confratello incaricato.</t>
+  </si>
+  <si>
+    <t>Le pensioni che provengono al Religioso per lavoro, per convenzione o altra ragione, pertinenti esclusivamente al periodo antecedente l’ingresso nella vita religiosa, fanno parte del suo patrimonio e vengono regolate a norma del can. 668 3 del CIC e dell’art. 95 delle Costituzioni.
+Le pensioni che provengono al Religioso per lavoro svolto nel tempo trascorso nella vita religiosa, o per circostanze o condizioni pertinenti al medesimo tempo, e le pensioni dette in Italia “sociali” fanno parte dei beni comuni e saranno versate alla casa cui appartiene o alla casa generale, a giudizio del Superiore generale.
+E’ vivamente raccomandato che, ove si verifichino le necessarie condizioni, vengano compiute le prosecuzioni volontarie per far maturare i diritti alle pensioni. In questi casi se un Religioso ha iniziato forme assicurative prima di entrare nella vita religiosa, concorderà con il Superiore generale gli oneri della prosecuzione volontaria e il godimento della pensione; se, al contrario, la prosecuzione volontaria avviene per forme assicurative iniziate dopo l’ingresso nella vita religiosa, gli oneri assicurativi sono a carico della casa generale e alla stessa verranno versati i godimenti della pensione, salvo eccezioni a giudizio del Superiore generale in favore della casa cui appartiene il confratello.
+In casi dubbi o non previsti da quanto sopra esposto, saranno rimessi alla decisione del Superiore generale.</t>
+  </si>
+  <si>
+    <t>Imitando l’esempio del Frassinetti, in tutte le relazioni, sia in casa che fuori, i Figli di S. Maria Immacolata mantengono sempre quel dignitoso riserbo che è proprio di chi attende alla perfezione religiosa e ha il dovere di testimoniare, soprattutto con l’esempio, l’eccellenza di questa virtù.
+Ognuno cercherà di guardarsi anche da quanto potrebbe ingenerare agli occhi altrui qualche ombra al riguardo.</t>
+  </si>
+  <si>
+    <t>Sappiano far tesoro delle occasioni che offrono la possibilità di praticare in concreto la virtù dell’obbedienza, superando le umane riluttanze con spirito di sacrificio.
+Quando si riceve l’ordine di mutare casa o ufficio, si attui l’obbedienza con generosità, anche se non appaiono evidenti i motivi dell’ordine ricevuto.</t>
+  </si>
+  <si>
+    <t>I confratelli pratichino specialmente la carità fraterna, siano l’un l’altro di reciproca emulazione nella pratica delle virtù religiose ed accolgano con umiltà e gratitudine la correzione fraterna, fatta loro secondo lo spirito del Vangelo.
+Si mostrino sempre, con tutti, sereni, comprensivi e fraternamente aperti.</t>
+  </si>
+  <si>
+    <t>Si raccomanda che nella parte della casa riservata ai religiosi, eccetto che per lavori e pulizie, non siano ammesse persone estranee alla comunità.
+Per le ripetizioni a persone singole siano destinati, dal Superiore o da chi di dovere , locali soggetti a controllo.</t>
+  </si>
+  <si>
+    <t>E’ opportuno che tutti i Religiosi trascorrano nell’anno un periodo di vacanze per complessivi 20 giorni, in famiglia o in case della Congregazione, oppure in altro luogo di soggiorno concordato con il Superiore locale e la comunità. I confratelli Sacerdoti e i Fratelli professi che risiedono fuori dal proprio continente trascorreranno ogni due anni un periodo di 30 giorni nella propria nazione, Per le vacanze sarà elargita ai confratelli una congrua somma del cui impiego renderanno poi conto al Superiore. La somma per le vacanze, eccettuata quella del viaggio, sia uguale per tutti i confratelli e sia stabilita dal Consiglio Superiore.
+Le vacanze degli studenti professi, sia in patria che nelle nostre comunità, essendo un periodo positivo nell’iter formativo del giovane religioso, saranno regolamentate dal Consiglio Superiore in accordo con il Formatore.</t>
+  </si>
+  <si>
+    <t>Non si viaggi se non per giusti motivi, evitando spese non richieste dalla necessità e non consone alla povertà.
+Se i confratelli si fermeranno in luoghi ove esiste una nostra casa, preferibilmente alloggeranno in essa.</t>
+  </si>
+  <si>
+    <t>L’Istituto di educazione e istruzione è affidato all’intera comunità religiosa educante.
+Essa è costituita in forma primaria dai Religiosi che operano nell’istituto, affiancati in un rapporto di collaborazione e integrazione dai laici che, a vario titolo, sono coinvolti nell’opera educativa e formativa dell’istituto stesso.</t>
+  </si>
+  <si>
+    <t>Negli istituti di istruzione vi sia possibilmente un preside per le scuole di 1° grado, un preside per le scuole di 2° grado e un responsabile per le scuole elementari.
+Essi sono nominati dal Superiore generale e suo Consiglio, sentito il parere del Superiore locale.</t>
+  </si>
+  <si>
+    <t>Le nostre parrocchie sono determinate comunità di fedeli in cui si rende visibile in un certo modo la Chiesa universale e la cui cura pastorale è affidata dal Vescovo diocesano alla Congregazione dei Figli di Santa Maria Immacolata.
+I Superiori delegheranno ad essa dei Religiosi che con la loro preghiera, vita comunitaria e osservanza dei voti religiosi attueranno la prima ed essenziale forma di evangelizzazione.</t>
+  </si>
+  <si>
+    <t>Si tenga presente che nella parrocchia affidata, per mezzo della Congregazione, ad una comunità religiosa, tutti i confratelli sono corresponsabili della cura pastorale. Giuridicamente però un Religioso sarà designato come parroco e gli altri come vicari parrocchiali. Ai Religiosi addetti alla cura pastorale si garantisca una certa stabilità, ma si riconosce anche molto opportuno l’avvicendamento, tenendo presente il bene della Congregazione, le esigenze della parrocchia, l’orientamento degli episcopati nazionali.
+Tuttavia è bene stare sempre alla retta intenzione e al discernimento del Superiore generale.</t>
+  </si>
+  <si>
+    <t>Ogni comunità deve darsi una pastorale concordata e studiata all’interno della comunità stessa nella quale si evidenzieranno con forza, anche attraverso le visite del Superiore generale, gli elementi fondamentali del carisma della Congregazione.
+Non si potrà mai disattendere che, in ultima istanza, chi renderà visibile e tangibile il carisma della Congregazione sarà sempre il Figlio di Maria come testimone con le parole e con il suo stile di vita.</t>
+  </si>
+  <si>
+    <t>I rapporti tra comunità religiosa ed ente parrocchia saranno regolati dalla relativa convenzione tra Vescovo e Congregazione. Casi particolari saranno risolti dal Superiore generale e suo Consiglio, sentito il parere della comunità religiosa. Nelle spese straordinarie il parroco, oltre alle autorizzazioni scritte da parte del Vescovo, consulti il Superiore locale e, se fossero di notevole impegno, anche il Consiglio generale.
+Non è lecito ai parroci contrarre impegni, servitù, contratti di qualsiasi genere su immobili della parrocchia, senza l’autorizzazione scritta dell’Ordinario diocesano, segnalando preventivamente la situazione al Superiore generale.
+Detto obbligo ricorre anche nelle variazioni di confine o di finalità dell’opera.</t>
+  </si>
+  <si>
+    <t>I registri canonici saranno aggiornati e curati secondo le norme dell’Ordinario diocesano. Si tenga aggiornata la cronaca degli avvenimenti principali della parrocchia. Per questi si usino gli accorgimenti tecnici che si riterranno più idonei.
+E’ auspicabile per la corrispondenza di ufficio parrocchiale l’uso del registro protocollo.</t>
+  </si>
+  <si>
+    <t>Le case particolari attenderanno alle opere cui sonno state destinate. Non si potranno iniziare altre opere, nell’interno o fuori di dette case, sopprimere quelle esistenti o comunque modificarne lo scopo senza il consenso del Consiglio superiore.
+Lo stesso deve essere ragguagliato tempestivamente qualora si verifichino eventi che possano comprometterne l’efficienza, l’economia e le finalità.</t>
+  </si>
+  <si>
+    <t>Con particolare cura preparerà la relazione annuale da inviare al Consiglio superiore, secondo le indicazioni fissate dal Capitolo o dal Consiglio stesso.
+La suddetta relazione si invii unitamente al bilancio consuntivo e preventivo della casa.</t>
+  </si>
+  <si>
+    <t>Il Superiore, responsabile della comunità, vigilerà affinché i laici in qualche modo operanti alle dipendenze nelle nostre opere, siano di retti principi religiosi, di onesta condotta morale e, se conviventi nelle nostre case, disponibili all’osservare gli ordinamenti della casa stessa.
+Ciò sia ben chiaro nel contratto di assunzione e sia convenuto come ragione valida di licenziamento in caso di inosservanza.</t>
+  </si>
+  <si>
+    <t>Spetta al Superiore generale e suo Consiglio, sentito prima il candidato, compiere la nomina del Legale Rappresentante.
+Potrà essere nominato un Legale Rappresentante per ogni Ente giuridico, oppure più Enti giuridici potranno essere rappresentanti da un solo incaricato.</t>
+  </si>
+  <si>
+    <t>Il Legale Rappresentante rappresenta l’Ente religioso agli effetti giuridici e agisce in suo nome, tenendo presente che per il compimento di atti di straordinaria amministrazione (acquisti, vendite, locazioni, ipoteche, mutui...) o di particolare interesse, è necessaria l’autorizzazione del Superiore competente, secondo le Costituzioni e il Direttorio, nonché della Santa Sede, laddove è prescritta.
+Si ponga particolare attenzione al rilievo giuridico del Legale Rappresentante per tutti gli atti di sua competenza e sia debitamente consultato.</t>
+  </si>
+  <si>
+    <t>Fermi restando gli obblighi e le scadenze fissate da leggi civili ed ecclesiastiche per l’attività ad esse soggette, l’esercizio finanziario per le opere della Congregazione seguirà l’anno solare.
+Per casi particolari, come gli istituti di istruzione, il Superiore generale e suo Consiglio potranno decidere diversamente.
+Il rendiconto annuale dell’esercizio finanziario e suo riscontro cassa documentato sarà inviato al Consiglio superiore entro tre mesi dalla scadenza secondo le forme indicate dalla Congregazione.</t>
+  </si>
+  <si>
+    <t>Il contributo alla Cassa generale delle singole opere sarà annualmente stabilito dal Superiore generale e suo Consiglio, casa per casa, tenendo conto degli utili (e delle perdite) dell’anno precedente e del suo stato patrimoniale.
+Le comunità siano sensibili alle esigenze della Congregazione, rispondendo con vero spirito religioso a quanto viene loro richiesto.</t>
+  </si>
+  <si>
+    <t>In ogni rapporto con i fornitori, ente, familiari degli alunni e con il personale di servizio l’Economo sappia manifestare sempre le più belle qualità umane e religiose, specie la gentilezza e la comprensione.
+Ciò non gli impedirà di salvaguardare i diritti della casa religiosa, anzi gli renderà più facile il suo compito, dandogli l’occasione di offrire buona testimonianza religiosa. Sappia specialmente dare egli stesso grande importanza alle virtù della giustizia e della carità.</t>
+  </si>
+  <si>
+    <t>Al Superiore generale è lasciata facoltà di dispensare temporaneamente e per giusti e proporzionati motivi, tutta la Congregazione da qualcuna di esse.
+La stessa facoltà e dentro gli stessi limiti è concessa al Superiore locale per la sua comunità.</t>
+  </si>
+  <si>
+    <t>Siano costituite in tutte le case o istituti d’educazione e di istruzione le associazioni degli ex-allievi per continuare l’opera di formazione in vista dell’azione educativa da estendere nelle loro famiglie.
+La comunità demandi al Religioso ritenuto più idoneo l’assistenza dell’associazione.</t>
+  </si>
+  <si>
+    <t>a. la formazione comune che riguarda tutti gli alunni e si attua nelle pratiche comuni di pietà: vita sacramentale, santa Messa, meditazione, esercizi spirituali, ecc.;
+b. la formazione personale che riguarda il singolo alunno e che si attua con il colloquio, la confessione, la direzione spirituale propriamente detta;
+c. la formazione specializzata che raggiunge quei gruppi di alunni che desiderano impegnarsi più attivamente nella vita di apostolato e di perfezione.</t>
+  </si>
+  <si>
+    <t>D) Il Padre Spirituale</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Il Padre spirituale terrà in massima considerazione e stima il suo ufficio e vi si dedicherà invocando l’aiuto del Signore e applicandovisi con diligenza e sacrificio. Procurerà de perfezionare continuamente quelle doti soprannaturali e naturali che gli permettano un più facile avvicinamento ai giovani, quali la sensibilità psicologica, l’apertura umana del cuore, l’equilibrio interiore, la sua vita spirituale stessa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triplice è il suo compito:
+</t>
+  </si>
+  <si>
+    <t>Cercherà, con i mezzi più idonei e più comprovati dalla scienza pastorale e dall’esperienza, di ottenere una convinta formazione cristiana dei giovani, cosicché sia assicurato un prosieguo di vita integralmente conforme ai principi del Vangelo.</t>
+  </si>
+  <si>
+    <t>Con tatto e prudenza procuri che i ragazzi partecipino volenterosamente e consapevolmente anche alle necessarie pratiche comuni da compiersi in corrispondenza alle esigenze dell’età evolutiva dei giovani stessi.</t>
+  </si>
+  <si>
+    <t>Egli dovrà favorire le devozioni specifiche e tradizionali dei Figli di S. Maria Immacolata, quali la devozione al S. Cuore, all’Immacolata, a S. Giuseppe e S. Pio X.</t>
+  </si>
+  <si>
+    <t>Previa intesa con il Superiore, curerà l’organizzazione di incontri e si varrà di altri mezzi idonei a tenere la vita spirituale dei ragazzi nel periodo delle vacanze.
+Avrà premure particolari per gli alunni infermi.</t>
+  </si>
+  <si>
+    <t>Vi sia piena collaborazione tra il Superiore e gli altri confratelli preposti alle varie attività della casa e il padre spirituale, cosicché non si frappongano reciproci impedimento, ma si consegua più facilmente il comune intento dell’integrale formazione del giovane.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Il Padre spirituale nei nostri istituti è il consigliere e la guida spirituale degli alunni e il collaboratore ordinario del Superiore per l’organizzazione delle attività religiose dei giovani.</t>
+  </si>
+  <si>
+    <t>Si accantoni per ciascuno ogni anno almeno una mensualità del loro stipendio, al fine di costituire un adeguato fondo di liquidazione. Se qualcuno dovesse essere licenziato, gli si dia il necessario preavviso, secondo contratto, gli si liquidino con giustizia tutte le sue spettanze e si procuri di rimanere con lui in buone relazioni di amicizia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All’atto della loro assunzione sia stipulato un regolare contratto di lavoro, secondo il modulo della categoria e si osservino tutte le prescrizioni di leggere per quanto concerne le assicurazioni sociali e il trattamento economico.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Con opportune istruzioni si curi:
+</t>
+  </si>
+  <si>
+    <t>•. che siano animati da spirito di apostolato, base indispensabile di ogni efficace azione educativa ed istruttiva;
+•. che sentano l’altezza del loro compito e lo compiano con dignità e competenza, nella convinzione che è soprattutto con l’esempio che si formano i giovani.</t>
+  </si>
+  <si>
+    <t>C) Inseganti laici</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gli insegnanti laici, preziosi collaboratori nelle nostre scuole, siano scelti tra persone non solo qualificate professionalmente, ma anche di elevati sentimenti morali e religiosi e di condotta seria e dignitosa.
+</t>
+  </si>
+  <si>
+    <t>Spetta al preside l’accettazione e il licenziamento degli insegnanti e degli alunni, sentito prima il parere e le proposte del Superiore e dell’Economo.</t>
+  </si>
+  <si>
+    <t>Sia i presidi i responsabili della scuola elementare riferiscano al Superiore sull’attività didattica degli insegnanti e sull’andamento didattico e disciplinare della scuola.</t>
+  </si>
+  <si>
+    <t>L’insegnamento della religione, anima e direttiva costante del nostro sistema educativo, sarà inserto nell’orario scolastico e attuato in due ore settimanali, specie nelle classi superiori.
+Ad esso saranno assegnati insegnanti ben preparati anche didatticamente ed efficacemente sostenuti dalla presidenza. Quanto è stato detto per i presidi vale anche per i responsabili delle scuole elementari.</t>
+  </si>
+  <si>
+    <t>B) I Presidi</t>
+  </si>
+  <si>
+    <t>Qualora situazioni particolari richiedessero di affiancare al Superiore un altro confratello che assuma responsabilità specifiche nella coordinazione dell’attività dell’istituto, il Superiore generale, consultato il Superiore della casa, provvederà a nominare un confratello a tale scopo.</t>
+  </si>
+  <si>
+    <t>In ogni circostanza si comporti in maniera da ispirare confidenza e fiducia. Si adoperi nell’eliminare, anzi prevenire, ogni causa di giustificato malcontento fra gli alunni.</t>
+  </si>
+  <si>
+    <t>A) Il Superiore</t>
+  </si>
+  <si>
+    <t>Per la parte disciplinare eserciterà una generale vigilanza senza intervenire direttamente nelle cose secondarie e minute affidate ai suoi collaboratori.
+Avrà fiducia in loro e concederà la libertà d’azione nell’ambito del loro ufficio, curando che lo adempiano con esattezza.</t>
+  </si>
+  <si>
+    <t>Il Superiore con la generosa e fattiva collaborazione di tutta la comunità darà grande importanza alla vita spirituale favorendo la partecipazione degli alunni alla celebrazione dell’Eucarestia, la frequenza ai Sacramenti, ai momenti di preghiera e di adorazione e la devozione filiale a Maria Immacolata.</t>
+  </si>
+  <si>
+    <t>Gli alunni del convitto dipendono dal Superiore, al quale spettano anche l’accettazione e il licenziamento di essi come pure il trattare con i loro parenti e tutori.
+Le rette e i criteri per le eventuali riduzioni ad alunni meritevoli ma bisognosi saranno stabilite d’intesa con la comunità.</t>
+  </si>
+  <si>
+    <t>Il Superiore si adoperi perché tra i presidi regni la più cordiale collaborazione per l’unità educativa dell’istituto e per il coordinamento delle varie attività dell’anno scolastico.</t>
+  </si>
+  <si>
+    <t>Il Superiore assumerà anche la funzione di gestore “durante munere” dell’istituto scolastico annesso alla casa religiosa.</t>
+  </si>
+  <si>
+    <t>Si regolerà in tutto secondo le mansioni e le responsabilità attribuitegli dalle Costituzioni e dal presente Direttorio.</t>
+  </si>
+  <si>
+    <t>Ricordando lo scopo vocazionale della nostra Congregazione, il Superiore procuri di favorire le vocazioni sacerdotali e religiose, appoggiando le iniziative dei vocazionisti e del padre spirituale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> E’ compito specifico del Superiore dare precisi indirizzi perché l’istituto consegua il fine a cui è destinato e accertarsi che l’insegnamento impartito nella scuola sia in linea con il nostro carisma ed in armonia con le più sane tradizioni della scuola cattolica secondo le indicazioni del magistero della Chiesa e delle Conferenze Episcopali.</t>
+  </si>
+  <si>
+    <t>Nella direzione e governo dell’istituto, il Superiore dovrà procedere d’intesa con i suoi collaboratori nella programmazione delle attività fondamentali e del lavoro dei confratelli.</t>
+  </si>
+  <si>
+    <t>Il Superiore è il coordinatore dell’andamento spirituale, scolastico, disciplinare ed economico dell’istituto. I confratelli chiamati a collaborare con lui sono responsabili ciascuno del proprio ufficio: “Tale autonomia però non è assoluta: implica sempre obbedienza responsabile e ordinata e comporta il collegamento con l’autorità del Superiore e la dipendenza da essa” (cfr. art. 194 delle Costituzioni).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I Presidi adempiano il loro ufficio in conformità alle leggi vigenti e alle direttive delle superiori autorità religiose.
+Curino, secondo il progetto educativo della Congregazione, la formazione degli alunni e la sensibilità degli insegnanti esterni per l’apostolato cristiano della scuola.
+Il vice-preside sia di preferenza un insegnante religioso della comunità, con firma depositata al provveditorato.
+</t>
+  </si>
+  <si>
+    <t>Nelle relazioni con le autorità ecclesiastiche, religiose e civili il parroco e i suoi collaboratori si mostrino rispettosi.
+Nei rapporti con la popolazione si mantengano il più possibile al di sopra dei partiti e delle competizioni politiche. Tengano conto che la scelta preferenziale della Chiesa è verso i poveri.</t>
+  </si>
+  <si>
+    <t>Sia impegno caratteristico delle parrocchie dei Figli di S. Maria Immacolata curare una pastorale vocazionale non solo di annuncio deciso dei valori cristiani fondamentali, ma anche di accompagnamento attraverso la direzione spirituale.
+Si studino anche iniziative per valorizzare tutto ciò che può favorire una crescita di coscienza vocazionale nei fedeli.
+Si raccomanda l’ascolto dei suggerimenti proposti dai nostri responsabili vocazionali.</t>
+  </si>
+  <si>
+    <t>Seguendo le indicazioni del Papa e dei Vescovi, si abbia un atteggiamento di apertura e di accettazione nei confronti dei movimenti ecclesiali tendenti a vitalizzare il laicato cattolico, vedendo in essi degli strumenti pastorali suscitati dallo Spirito Santo e adeguati al nostro tempo. 
+Tuttavia i Religiosi si ricordino di essere i pastori di tutto il gregge di Dio a loro affidato, non assolutizzando le varie esperienze. Si fa presente la necessità della cura sistematica ed attenta dei gruppi giovanili della parrocchia affinché ogni seme di vocazione venga riconosciuto e curato.</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11CDCDEF-D492-46D8-852B-98D05B6EA954}">
-  <dimension ref="A1:G223"/>
+  <dimension ref="A1:G230"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="28.77734375" customWidth="1"/>
@@ -1306,8 +1314,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
+    <row r="2" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
@@ -1319,42 +1329,48 @@
       </c>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
+    <row r="3" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
@@ -1364,10 +1380,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2" t="s">
@@ -1381,10 +1397,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
@@ -1398,10 +1414,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
@@ -1415,10 +1431,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
@@ -1432,10 +1448,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2" t="s">
@@ -1443,16 +1459,16 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>17</v>
+        <v>200</v>
       </c>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
@@ -1460,16 +1476,16 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>18</v>
+        <v>201</v>
       </c>
       <c r="G11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
@@ -1477,16 +1493,16 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G12" s="2"/>
     </row>
     <row r="13" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
@@ -1494,16 +1510,16 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
@@ -1511,16 +1527,16 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>202</v>
       </c>
       <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
@@ -1528,16 +1544,16 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
-        <v>22</v>
+        <v>203</v>
       </c>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
@@ -1545,16 +1561,16 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
@@ -1562,16 +1578,16 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="s">
-        <v>24</v>
+        <v>205</v>
       </c>
       <c r="G17" s="2"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2" t="s">
@@ -1579,1338 +1595,1336 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="2" t="s">
-        <v>25</v>
+        <v>206</v>
       </c>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>10</v>
+        <v>199</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1</v>
+      </c>
       <c r="F19" s="2" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>10</v>
+        <v>199</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
       <c r="F20" s="2" t="s">
-        <v>27</v>
+        <v>208</v>
       </c>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>10</v>
+        <v>199</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E21" s="2">
+        <v>3</v>
+      </c>
       <c r="F21" s="2" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+      <c r="G22" s="2"/>
+    </row>
+    <row r="23" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E23" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="G23" s="2"/>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="G24" s="2"/>
     </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="G25" s="2"/>
+    </row>
+    <row r="26" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="G27" s="2"/>
     </row>
-    <row r="28" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="2">
         <v>7</v>
       </c>
+      <c r="E28" s="2"/>
       <c r="F28" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="G28" s="2"/>
     </row>
-    <row r="29" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="2">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="2">
-        <v>8</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G30" s="2"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E31" s="2">
+        <v>12</v>
+      </c>
       <c r="F31" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G31" s="2"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E32" s="2">
+        <v>13</v>
+      </c>
       <c r="F32" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="G32" s="2"/>
     </row>
-    <row r="33" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G33" s="2"/>
     </row>
-    <row r="34" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="G34" s="2"/>
     </row>
-    <row r="35" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G35" s="2"/>
     </row>
-    <row r="36" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E36" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>47</v>
+        <v>210</v>
       </c>
       <c r="G36" s="2"/>
     </row>
     <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="G37" s="2"/>
     </row>
-    <row r="38" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="G38" s="2"/>
     </row>
-    <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G39" s="2"/>
     </row>
-    <row r="40" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+      <c r="G40" s="2"/>
+    </row>
+    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E41" s="2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="G41" s="2"/>
     </row>
-    <row r="42" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E42" s="2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>54</v>
+        <v>211</v>
       </c>
       <c r="G42" s="2"/>
     </row>
-    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E43" s="2">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G43" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="44" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G44" s="2"/>
     </row>
-    <row r="45" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E45" s="2">
-        <v>22</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E45" s="2"/>
       <c r="F45" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2"/>
     </row>
-    <row r="46" spans="1:7" ht="216" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E46" s="2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="G46" s="2"/>
+    </row>
+    <row r="47" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E47" s="2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E49" s="2">
+        <v>29</v>
+      </c>
       <c r="F49" s="2" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E50" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E50" s="2">
+        <v>30</v>
+      </c>
       <c r="F50" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2"/>
     </row>
-    <row r="51" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="G51" s="2"/>
     </row>
-    <row r="52" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E52" s="2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E53" s="2">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G53" s="2"/>
     </row>
-    <row r="54" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E54" s="2">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="G54" s="2"/>
     </row>
-    <row r="55" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E55" s="2">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="G55" s="2"/>
     </row>
     <row r="56" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="G56" s="2"/>
     </row>
-    <row r="57" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E57" s="2">
-        <v>32</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E57" s="2"/>
       <c r="F57" s="2" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G57" s="2"/>
     </row>
-    <row r="58" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E58" s="2">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="G58" s="2"/>
     </row>
-    <row r="59" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="G59" s="2"/>
     </row>
     <row r="60" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G60" s="2"/>
     </row>
-    <row r="61" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E61" s="2">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="G61" s="2"/>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E62" s="2">
+        <v>41</v>
+      </c>
       <c r="F62" s="2" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="G62" s="2"/>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E63" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E63" s="2">
+        <v>42</v>
+      </c>
       <c r="F63" s="2" t="s">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="G63" s="2"/>
     </row>
-    <row r="64" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E64" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="G64" s="2"/>
     </row>
-    <row r="65" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E65" s="2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="G65" s="2"/>
     </row>
-    <row r="66" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E66" s="2">
-        <v>39</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E66" s="2"/>
       <c r="F66" s="2" t="s">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="G66" s="2"/>
     </row>
     <row r="67" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E67" s="2">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E68" s="2">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G68" s="2"/>
     </row>
-    <row r="69" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E69" s="2">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E70" s="2">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="G70" s="2"/>
     </row>
-    <row r="71" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E71" s="2">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E72" s="2">
+        <v>50</v>
+      </c>
       <c r="F72" s="2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="G72" s="2"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E73" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E73" s="2">
+        <v>51</v>
+      </c>
       <c r="F73" s="2" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="G73" s="2"/>
     </row>
-    <row r="74" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E74" s="2">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="G74" s="2"/>
     </row>
-    <row r="75" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>88</v>
+        <v>65</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E75" s="2">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="G75" s="2"/>
     </row>
-    <row r="76" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E76" s="2">
-        <v>47</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E76" s="2"/>
       <c r="F76" s="2" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G76" s="2"/>
     </row>
-    <row r="77" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E77" s="2">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>93</v>
+        <v>214</v>
       </c>
       <c r="G77" s="2"/>
     </row>
-    <row r="78" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E78" s="2">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="G78" s="2"/>
     </row>
-    <row r="79" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E79" s="2">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="G79" s="2"/>
     </row>
-    <row r="80" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E80" s="2">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="G80" s="2"/>
     </row>
-    <row r="81" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E81" s="2">
-        <v>52</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E81" s="2"/>
       <c r="F81" s="2" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="G81" s="2"/>
     </row>
-    <row r="82" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E82" s="2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="G82" s="2"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E83" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E83" s="2">
+        <v>59</v>
+      </c>
       <c r="F83" s="2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="G83" s="2"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E84" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E84" s="2">
+        <v>60</v>
+      </c>
       <c r="F84" s="2" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="G84" s="2"/>
     </row>
-    <row r="85" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E85" s="2">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="G85" s="2"/>
+    </row>
+    <row r="86" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E86" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="G86" s="2"/>
     </row>
-    <row r="87" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E87" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G87" s="2"/>
     </row>
-    <row r="88" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E88" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="G88" s="2"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2" t="s">
@@ -2918,166 +2932,170 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" s="2" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="G89" s="2"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E90" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E90" s="2">
+        <v>65</v>
+      </c>
       <c r="F90" s="2" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="G90" s="2"/>
     </row>
-    <row r="91" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E91" s="2">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="G91" s="2"/>
     </row>
-    <row r="92" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E92" s="2">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="G92" s="2"/>
     </row>
-    <row r="93" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E93" s="2">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="G93" s="2"/>
     </row>
-    <row r="94" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E94" s="2">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="G94" s="2"/>
     </row>
     <row r="95" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E95" s="2">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>112</v>
+        <v>217</v>
       </c>
       <c r="G95" s="2"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E96" s="2">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="G96" s="2"/>
     </row>
-    <row r="97" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E97" s="2">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G97" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="98" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2" t="s">
@@ -3085,16 +3103,16 @@
       </c>
       <c r="E98" s="2"/>
       <c r="F98" s="2" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="G98" s="2"/>
     </row>
-    <row r="99" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2" t="s">
@@ -3102,1949 +3120,1989 @@
       </c>
       <c r="E99" s="2"/>
       <c r="F99" s="2" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="G99" s="2"/>
     </row>
     <row r="100" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E100" s="2">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>118</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="G100" s="2"/>
     </row>
     <row r="101" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E101" s="2">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="G101" s="2"/>
     </row>
-    <row r="102" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E102" s="2">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+      <c r="G102" s="2"/>
+    </row>
+    <row r="103" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E103" s="2">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="G103" s="2"/>
     </row>
-    <row r="104" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E104" s="2">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="G104" s="2"/>
     </row>
-    <row r="105" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E105" s="2">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+      <c r="G105" s="2"/>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E106" s="2">
-        <v>71</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E106" s="2"/>
       <c r="F106" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="G106" s="2"/>
     </row>
-    <row r="107" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E107" s="2">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G107" s="2"/>
     </row>
     <row r="108" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E108" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E108" s="2">
+        <v>81</v>
+      </c>
       <c r="F108" s="2" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="G108" s="2"/>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E109" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E109" s="2">
+        <v>82</v>
+      </c>
       <c r="F109" s="2" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="G109" s="2"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E110" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E110" s="2">
+        <v>83</v>
+      </c>
       <c r="F110" s="2" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="G110" s="2"/>
     </row>
-    <row r="111" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E111" s="2">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="G111" s="2"/>
     </row>
-    <row r="112" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E112" s="2">
-        <v>75</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E112" s="2"/>
       <c r="F112" s="2" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="G112" s="2"/>
     </row>
-    <row r="113" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E113" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="G113" s="2"/>
     </row>
-    <row r="114" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E114" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="G114" s="2"/>
     </row>
-    <row r="115" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E115" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="G115" s="2"/>
     </row>
-    <row r="116" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E116" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="G116" s="2"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E117" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E117" s="2">
+        <v>89</v>
+      </c>
       <c r="F117" s="2" t="s">
-        <v>138</v>
+        <v>234</v>
       </c>
       <c r="G117" s="2"/>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C118" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D118" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E118" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E118" s="2">
+        <v>90</v>
+      </c>
       <c r="F118" s="2" t="s">
-        <v>139</v>
+        <v>267</v>
       </c>
       <c r="G118" s="2"/>
     </row>
-    <row r="119" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C119" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D119" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E119" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>140</v>
+        <v>266</v>
       </c>
       <c r="G119" s="2"/>
     </row>
-    <row r="120" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C120" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D120" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E120" s="2">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>141</v>
+        <v>265</v>
       </c>
       <c r="G120" s="2"/>
     </row>
-    <row r="121" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C121" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D121" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E121" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>142</v>
+        <v>264</v>
       </c>
       <c r="G121" s="2"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C122" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D122" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E122" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>143</v>
+        <v>263</v>
       </c>
       <c r="G122" s="2"/>
     </row>
-    <row r="123" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D123" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E123" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>144</v>
+        <v>262</v>
       </c>
       <c r="G123" s="2"/>
     </row>
-    <row r="124" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D124" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E124" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E124" s="2">
+        <v>96</v>
+      </c>
       <c r="F124" s="2" t="s">
-        <v>145</v>
+        <v>261</v>
       </c>
       <c r="G124" s="2"/>
     </row>
-    <row r="125" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C125" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D125" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E125" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E125" s="2">
+        <v>97</v>
+      </c>
       <c r="F125" s="2" t="s">
-        <v>146</v>
+        <v>260</v>
       </c>
       <c r="G125" s="2"/>
     </row>
-    <row r="126" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D126" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E126" s="2">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+      <c r="G126" s="2"/>
+    </row>
+    <row r="127" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C127" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D127" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E127" s="2">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>258</v>
+      </c>
+      <c r="G127" s="2"/>
+    </row>
+    <row r="128" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C128" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D128" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E128" s="2">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>151</v>
+        <v>256</v>
       </c>
       <c r="G128" s="2"/>
     </row>
     <row r="129" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C129" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="D129" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E129" s="2">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>152</v>
+        <v>255</v>
       </c>
       <c r="G129" s="2"/>
     </row>
-    <row r="130" spans="1:7" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C130" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="D130" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E130" s="2">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+        <v>268</v>
+      </c>
+      <c r="G130" s="2"/>
+    </row>
+    <row r="131" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C131" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="D131" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E131" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E131" s="2">
+        <v>103</v>
+      </c>
       <c r="F131" s="2" t="s">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="G131" s="2"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C132" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="D132" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E132" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E132" s="2">
+        <v>104</v>
+      </c>
       <c r="F132" s="2" t="s">
-        <v>156</v>
+        <v>252</v>
       </c>
       <c r="G132" s="2"/>
     </row>
-    <row r="133" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C133" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="D133" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E133" s="2">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+      <c r="G133" s="2"/>
+    </row>
+    <row r="134" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C134" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="D134" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E134" s="2">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>250</v>
+      </c>
+      <c r="G134" s="2"/>
+    </row>
+    <row r="135" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C135" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="D135" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E135" s="2">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C136" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="D136" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E136" s="2">
-        <v>121</v>
+        <v>108</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="G136" s="2"/>
     </row>
-    <row r="137" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C137" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="D137" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E137" s="2">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+      <c r="G137" s="2"/>
+    </row>
+    <row r="138" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C138" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D138" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E138" s="2">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+      <c r="G138" s="2"/>
+    </row>
+    <row r="139" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C139" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D139" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E139" s="2">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="G139" s="2"/>
     </row>
-    <row r="140" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C140" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D140" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E140" s="2">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G140" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="141" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C141" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D141" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E141" s="2">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>171</v>
-      </c>
+        <v>239</v>
+      </c>
+      <c r="G141" s="2"/>
     </row>
     <row r="142" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C142" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D142" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E142" s="2">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>172</v>
+        <v>240</v>
       </c>
       <c r="G142" s="2"/>
     </row>
-    <row r="143" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C143" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D143" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E143" s="2">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+      <c r="G143" s="2"/>
+    </row>
+    <row r="144" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C144" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D144" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E144" s="2">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="G144" s="2"/>
     </row>
-    <row r="145" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C145" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="D145" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E145" s="2">
-        <v>130</v>
+        <v>117</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="G145" s="2"/>
     </row>
-    <row r="146" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E146" s="2">
-        <v>131</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E146" s="2"/>
       <c r="F146" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+      <c r="G146" s="2"/>
+    </row>
+    <row r="147" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E147" s="2">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>179</v>
+        <v>220</v>
       </c>
       <c r="G147" s="2"/>
     </row>
-    <row r="148" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E148" s="2">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="G148" s="2"/>
-    </row>
-    <row r="149" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E149" s="2">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>181</v>
+        <v>221</v>
       </c>
       <c r="G149" s="2"/>
     </row>
-    <row r="150" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E150" s="2">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G150" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="G150" s="2"/>
+    </row>
+    <row r="151" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>155</v>
+        <v>118</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E151" s="2">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>184</v>
+        <v>269</v>
       </c>
       <c r="G151" s="2"/>
     </row>
-    <row r="152" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E152" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E152" s="2">
+        <v>123</v>
+      </c>
       <c r="F152" s="2" t="s">
-        <v>185</v>
+        <v>270</v>
       </c>
       <c r="G152" s="2"/>
     </row>
-    <row r="153" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E153" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E153" s="2">
+        <v>124</v>
+      </c>
       <c r="F153" s="2" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="G153" s="2"/>
     </row>
-    <row r="154" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E154" s="2">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>187</v>
+        <v>123</v>
       </c>
       <c r="G154" s="2"/>
     </row>
-    <row r="155" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E155" s="2">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="G155" s="2"/>
     </row>
-    <row r="156" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E156" s="2">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>189</v>
+        <v>124</v>
       </c>
       <c r="G156" s="2"/>
     </row>
-    <row r="157" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E157" s="2">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G157" s="2"/>
-    </row>
-    <row r="158" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E158" s="2">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="G158" s="2"/>
     </row>
-    <row r="159" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E159" s="2">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>192</v>
+        <v>128</v>
       </c>
       <c r="G159" s="2"/>
     </row>
-    <row r="160" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" ht="144" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E160" s="2">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>193</v>
+        <v>223</v>
       </c>
       <c r="G160" s="2"/>
     </row>
-    <row r="161" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E161" s="2">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="G161" s="2"/>
     </row>
-    <row r="162" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E162" s="2">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="G162" s="2"/>
     </row>
     <row r="163" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>185</v>
+        <v>118</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E163" s="2">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="G163" s="2"/>
     </row>
-    <row r="164" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E164" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E164" s="2">
+        <v>135</v>
+      </c>
       <c r="F164" s="2" t="s">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="G164" s="2"/>
     </row>
     <row r="165" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>197</v>
+        <v>118</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E165" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E165" s="2">
+        <v>136</v>
+      </c>
       <c r="F165" s="2" t="s">
-        <v>198</v>
+        <v>132</v>
       </c>
       <c r="G165" s="2"/>
     </row>
-    <row r="166" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E166" s="2">
-        <v>147</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E166" s="2"/>
       <c r="F166" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G166" s="2" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+      <c r="G166" s="2"/>
+    </row>
+    <row r="167" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E167" s="2">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>202</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="G167" s="2"/>
     </row>
     <row r="168" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E168" s="2">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>203</v>
+        <v>136</v>
       </c>
       <c r="G168" s="2"/>
     </row>
-    <row r="169" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E169" s="2">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>204</v>
+        <v>137</v>
       </c>
       <c r="G169" s="2"/>
     </row>
     <row r="170" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E170" s="2">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>205</v>
+        <v>138</v>
       </c>
       <c r="G170" s="2"/>
     </row>
-    <row r="171" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E171" s="2">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="G171" s="2"/>
     </row>
-    <row r="172" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E172" s="2">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="G172" s="2"/>
     </row>
-    <row r="173" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E173" s="2">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="G173" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+      <c r="G173" s="2"/>
+    </row>
+    <row r="174" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E174" s="2">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>210</v>
+        <v>142</v>
       </c>
       <c r="G174" s="2"/>
     </row>
     <row r="175" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E175" s="2">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>211</v>
+        <v>143</v>
       </c>
       <c r="G175" s="2"/>
     </row>
-    <row r="176" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E176" s="2">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>212</v>
+        <v>144</v>
       </c>
       <c r="G176" s="2"/>
     </row>
-    <row r="177" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>197</v>
+        <v>145</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E177" s="2">
-        <v>158</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E177" s="2"/>
       <c r="F177" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G177" s="2" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+      <c r="G177" s="2"/>
+    </row>
+    <row r="178" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E178" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E178" s="2">
+        <v>147</v>
+      </c>
       <c r="F178" s="2" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="G178" s="2"/>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E179" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E179" s="2">
+        <v>148</v>
+      </c>
       <c r="F179" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="G179" s="2"/>
-    </row>
-    <row r="180" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E180" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="G180" s="2"/>
     </row>
     <row r="181" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E181" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>218</v>
+        <v>150</v>
       </c>
       <c r="G181" s="2"/>
     </row>
-    <row r="182" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E182" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>219</v>
+        <v>151</v>
       </c>
       <c r="G182" s="2"/>
     </row>
-    <row r="183" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E183" s="2">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="G183" s="2"/>
     </row>
-    <row r="184" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E184" s="2">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>221</v>
+        <v>153</v>
       </c>
       <c r="G184" s="2"/>
     </row>
     <row r="185" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E185" s="2">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G185" s="2"/>
     </row>
-    <row r="186" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E186" s="2">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>223</v>
+        <v>154</v>
       </c>
       <c r="G186" s="2"/>
     </row>
-    <row r="187" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E187" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E187" s="2">
+        <v>156</v>
+      </c>
       <c r="F187" s="2" t="s">
-        <v>224</v>
+        <v>155</v>
       </c>
       <c r="G187" s="2"/>
     </row>
-    <row r="188" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E188" s="2">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>225</v>
+        <v>156</v>
       </c>
       <c r="G188" s="2"/>
     </row>
-    <row r="189" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E189" s="2">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G189" s="2" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="G189" s="2"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>224</v>
+        <v>157</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E190" s="2">
-        <v>168</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E190" s="2"/>
       <c r="F190" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+      <c r="G190" s="2"/>
+    </row>
+    <row r="191" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E191" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E191" s="2">
+        <v>159</v>
+      </c>
       <c r="F191" s="2" t="s">
-        <v>230</v>
+        <v>159</v>
       </c>
       <c r="G191" s="2"/>
     </row>
-    <row r="192" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E192" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E192" s="2">
+        <v>160</v>
+      </c>
       <c r="F192" s="2" t="s">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="G192" s="2"/>
     </row>
     <row r="193" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E193" s="2">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="G193" s="2"/>
     </row>
-    <row r="194" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E194" s="2">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>233</v>
+        <v>162</v>
       </c>
       <c r="G194" s="2"/>
     </row>
-    <row r="195" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E195" s="2">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>234</v>
+        <v>163</v>
       </c>
       <c r="G195" s="2"/>
     </row>
-    <row r="196" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E196" s="2">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G196" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
+        <v>164</v>
+      </c>
+      <c r="G196" s="2"/>
+    </row>
+    <row r="197" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E197" s="2">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+      <c r="G197" s="2"/>
+    </row>
+    <row r="198" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E198" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="G198" s="2"/>
     </row>
-    <row r="199" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E199" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="G199" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="G199" s="2"/>
+    </row>
+    <row r="200" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A200" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>230</v>
+        <v>166</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E200" s="2">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="G200" s="2"/>
     </row>
     <row r="201" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" s="2" t="s">
@@ -5052,430 +5110,563 @@
       </c>
       <c r="E201" s="2"/>
       <c r="F201" s="2" t="s">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="G201" s="2"/>
     </row>
-    <row r="202" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A202" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E202" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E202" s="2">
+        <v>170</v>
+      </c>
       <c r="F202" s="2" t="s">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="G202" s="2"/>
     </row>
-    <row r="203" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A203" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E203" s="2">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="G203" s="2"/>
     </row>
-    <row r="204" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A204" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E204" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="G204" s="2"/>
     </row>
-    <row r="205" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A205" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E205" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="G205" s="2"/>
     </row>
-    <row r="206" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A206" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E206" s="2">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G206" s="2"/>
-    </row>
-    <row r="207" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A207" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E207" s="2">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>249</v>
+        <v>175</v>
       </c>
       <c r="G207" s="2"/>
     </row>
-    <row r="208" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A208" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E208" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="G208" s="2"/>
     </row>
-    <row r="209" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A209" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>243</v>
+        <v>168</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E209" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="G209" s="2"/>
+    </row>
+    <row r="210" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A210" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>243</v>
+        <v>177</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E210" s="2">
-        <v>185</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E210" s="2"/>
       <c r="F210" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G210" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="G210" s="2"/>
+    </row>
+    <row r="211" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A211" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E211" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E211" s="2">
+        <v>178</v>
+      </c>
       <c r="F211" s="2" t="s">
-        <v>255</v>
+        <v>179</v>
       </c>
       <c r="G211" s="2"/>
     </row>
     <row r="212" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A212" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E212" s="2">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>256</v>
+        <v>180</v>
       </c>
       <c r="G212" s="2"/>
     </row>
-    <row r="213" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A213" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E213" s="2">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>257</v>
+        <v>181</v>
       </c>
       <c r="G213" s="2"/>
     </row>
-    <row r="214" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A214" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E214" s="2">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>258</v>
+        <v>182</v>
       </c>
       <c r="G214" s="2"/>
     </row>
-    <row r="215" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A215" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E215" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>259</v>
+        <v>183</v>
       </c>
       <c r="G215" s="2"/>
     </row>
     <row r="216" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A216" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E216" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>260</v>
+        <v>184</v>
       </c>
       <c r="G216" s="2"/>
     </row>
     <row r="217" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A217" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>255</v>
+        <v>177</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E217" s="2">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G217" s="2"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A218" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>262</v>
+        <v>177</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E218" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="E218" s="2">
+        <v>185</v>
+      </c>
       <c r="F218" s="2" t="s">
-        <v>262</v>
+        <v>232</v>
       </c>
       <c r="G218" s="2"/>
     </row>
-    <row r="219" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A219" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E219" s="2">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>263</v>
+        <v>188</v>
       </c>
       <c r="G219" s="2"/>
     </row>
-    <row r="220" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A220" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E220" s="2">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G220" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="G220" s="2"/>
+    </row>
+    <row r="221" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A221" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E221" s="2">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>266</v>
+        <v>190</v>
       </c>
       <c r="G221" s="2"/>
     </row>
     <row r="222" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A222" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E222" s="2">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>267</v>
+        <v>191</v>
       </c>
       <c r="G222" s="2"/>
     </row>
-    <row r="223" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A223" s="2" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>262</v>
+        <v>187</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E223" s="2">
+        <v>190</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="G223" s="2"/>
+    </row>
+    <row r="224" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A224" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C224" s="2"/>
+      <c r="D224" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E224" s="2">
+        <v>191</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="G224" s="2"/>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A225" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C225" s="2"/>
+      <c r="D225" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E225" s="2"/>
+      <c r="F225" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G225" s="2"/>
+    </row>
+    <row r="226" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A226" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C226" s="2"/>
+      <c r="D226" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E226" s="2">
+        <v>192</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="G226" s="2"/>
+    </row>
+    <row r="227" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A227" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C227" s="2"/>
+      <c r="D227" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E227" s="2">
+        <v>193</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G227" s="2"/>
+    </row>
+    <row r="228" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A228" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C228" s="2"/>
+      <c r="D228" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E228" s="2">
+        <v>194</v>
+      </c>
+      <c r="F228" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F223" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="G223" s="2"/>
+      <c r="G228" s="2"/>
+    </row>
+    <row r="229" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A229" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C229" s="2"/>
+      <c r="D229" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E229" s="2">
+        <v>195</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G229" s="2"/>
+    </row>
+    <row r="230" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A230" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C230" s="2"/>
+      <c r="D230" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E230" s="2">
+        <v>196</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G230" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G223" xr:uid="{11CDCDEF-D492-46D8-852B-98D05B6EA954}"/>
+  <autoFilter ref="A1:G230" xr:uid="{11CDCDEF-D492-46D8-852B-98D05B6EA954}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" orientation="portrait" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
